--- a/mixs-templates/Mimag_plus_combinations/MimagPlantAssociated.xlsx
+++ b/mixs-templates/Mimag_plus_combinations/MimagPlantAssociated.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EA1"/>
+  <dimension ref="A1:EC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,450 +624,460 @@
       </c>
       <c r="AP1" t="inlineStr">
         <is>
+          <t>marker_gene_recov</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>marker_gene_recov_sw</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
           <t>pos_cont_type</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>feat_pred</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>compl_software</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>env_local_scale</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>samp_mat_process</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>sim_search_meth</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>depth</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>samp_collect_method</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>compl_appr</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>env_medium</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>samp_taxon_id</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>geo_loc_name</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>collection_date</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>seq_meth</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>lat_lon</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>elev</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>env_broad_scale</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>tax_class</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>experimental_factor</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>associated_resource</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>sop</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>air_temp_regm</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>ances_data</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>antibiotic_regm</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>biol_stat</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>biotic_regm</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>chem_administration</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>chem_mutagen</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>climate_environment</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>cult_root_med</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>fertilizer_regm</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>fungicide_regm</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>gaseous_environment</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>genetic_mod</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>gravity</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>growth_facil</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>growth_habit</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>growth_hormone_regm</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>herbicide_regm</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>host_age</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>host_common_name</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>host_disease_stat</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>host_dry_mass</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>host_genotype</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>host_height</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>host_subspecf_genlin</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>host_length</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>host_life_stage</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>host_phenotype</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>host_taxid</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>host_tot_mass</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>host_wet_mass</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>humidity_regm</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>light_regm</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>mechanical_damage</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>mineral_nutr_regm</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>misc_param</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>non_min_nutr_regm</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>organism_count</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>oxy_stat_samp</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>ph_regm</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>perturbation</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>pesticide_regm</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>plant_growth_med</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>plant_product</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>plant_sex</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>plant_struc</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>radiation_regm</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>rainfall_regm</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>root_cond</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>root_med_carbon</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>root_med_macronutr</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>root_med_micronutr</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>root_med_suppl</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>root_med_ph</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>root_med_regl</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>root_med_solid</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>salt_regm</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>samp_capt_status</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>samp_dis_stage</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>salinity</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>samp_store_dur</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>samp_store_loc</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>samp_store_temp</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>season_environment</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>standing_water_regm</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>tiss_cult_growth_med</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>water_temp_regm</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>watering_regm</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>host_symbiont</t>
         </is>
@@ -1099,22 +1109,22 @@
     <dataValidation sqref="AK2:AK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"16S rRNA gene,multi-marker approach,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="AX2:AX1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AZ2:AZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"marker gene,other,reference based"</formula1>
     </dataValidation>
-    <dataValidation sqref="BN2:BN1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="BP2:BP1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"breeder's line,clonal selection,hybrid,inbred line,mutant,natural,semi-natural,wild"</formula1>
     </dataValidation>
-    <dataValidation sqref="BZ2:BZ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CB2:CB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"erect,prostrate,semi-erect,spreading"</formula1>
     </dataValidation>
-    <dataValidation sqref="CW2:CW1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="CY2:CY1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"aerobic,anaerobic,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="DP2:DP1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="DR2:DR1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"active surveillance in response to an outbreak,active surveillance not initiated by an outbreak,farm sample,market sample,other"</formula1>
     </dataValidation>
-    <dataValidation sqref="DQ2:DQ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="DS2:DS1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"dissemination,growth and reproduction,infection,inoculation,other,penetration"</formula1>
     </dataValidation>
   </dataValidations>
